--- a/01_Thermal/B_results/single_annular_bemt_tuning_report.xlsx
+++ b/01_Thermal/B_results/single_annular_bemt_tuning_report.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>order2_soft_rmse</t>
+          <t>order2_soft_cons</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -513,25 +513,25 @@
         <v>1.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H2" t="n">
         <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1515866004815027</v>
+        <v>0.1423867938031763</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06113027521512941</v>
+        <v>0.05573213054895053</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2534243753237843</v>
+        <v>0.2365781929295467</v>
       </c>
       <c r="L2" t="n">
         <v>1365</v>
@@ -543,7 +543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>order2_soft_cons</t>
+          <t>order2_soft_rmse</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -558,25 +558,25 @@
         <v>1.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H3" t="n">
         <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1516200464485156</v>
+        <v>0.1424606599512654</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06111445823481861</v>
+        <v>0.0557182025578135</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2541772488164116</v>
+        <v>0.2366546642235309</v>
       </c>
       <c r="L3" t="n">
         <v>1365</v>
@@ -615,13 +615,13 @@
         <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.152238268347096</v>
+        <v>0.1449856503944575</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05781424542819154</v>
+        <v>0.05357534864759952</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2626189176619134</v>
+        <v>0.2396380121492668</v>
       </c>
       <c r="L4" t="n">
         <v>1365</v>
@@ -660,13 +660,13 @@
         <v>1.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1533148118196686</v>
+        <v>0.1501090795013645</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05268504105720341</v>
+        <v>0.05078685451988883</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2699613080665096</v>
+        <v>0.2435602442291595</v>
       </c>
       <c r="L5" t="n">
         <v>1365</v>
@@ -705,13 +705,13 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1655620624387004</v>
+        <v>0.1633065485392445</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06205654570254396</v>
+        <v>0.05829619530803898</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2398745404558879</v>
+        <v>0.2348520580018477</v>
       </c>
       <c r="L6" t="n">
         <v>1365</v>
